--- a/AAII_Financials/Yearly/LSE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LSE_YR_FIN.xlsx
@@ -1624,7 +1624,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>20200</v>
+        <v>19100</v>
       </c>
       <c r="E43" s="3">
         <v>23700</v>
@@ -1684,7 +1684,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1100</v>
+        <v>2200</v>
       </c>
       <c r="E45" s="3">
         <v>700</v>
